--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536320_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536320_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1467,28 +1467,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5237</v>
+        <v>2.8155</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5956</v>
+        <v>1.8874</v>
       </c>
       <c r="F13" t="n">
         <v>0.9281</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5752</v>
+        <v>0.867</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4054</v>
+        <v>1.6972</v>
       </c>
       <c r="I13" t="n">
         <v>-0.8302</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2883</v>
+        <v>1.5801</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8006</v>
+        <v>2.0924</v>
       </c>
       <c r="L13" t="n">
         <v>-0.5123</v>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2918</v>
+        <v>-0.5029</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2918</v>
+        <v>1.0708</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.5738</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2918</v>
+        <v>1.9254</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2918</v>
+        <v>2.1879</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.2626</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2918</v>
+        <v>3.1168</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2918</v>
+        <v>3.6291</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5123</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.1914</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.4412</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.2497</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6439</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.5991</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.0295</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.5696</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-3.6438</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-1.048</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.5959</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5029</v>
+        <v>-1.0182</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0708</v>
+        <v>-0.5544</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5738</v>
+        <v>-0.4638</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9254</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1879</v>
+        <v>-1.2926</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2626</v>
+        <v>0.6642</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1168</v>
+        <v>-0.275</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6291</v>
+        <v>0.1167</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5123</v>
+        <v>-0.3917</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1914</v>
+        <v>-0.3535</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4412</v>
+        <v>-1.4093</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2497</v>
+        <v>1.0558</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6439</v>
+        <v>0.411</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5991</v>
+        <v>0.0281</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0295</v>
+        <v>-0.2795</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5696</v>
+        <v>0.3075</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.6438</v>
+        <v>-0.8288</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.048</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5959</v>
+        <v>-0.8288</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>A. YOUNG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0182</v>
+        <v>-2.0028</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5544</v>
+        <v>-3.9539</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4638</v>
+        <v>1.951</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-4.0783</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2926</v>
+        <v>-0.7343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6642</v>
+        <v>-3.344</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.275</v>
+        <v>-3.945</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1167</v>
+        <v>-0.4761</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3917</v>
+        <v>-3.4689</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3535</v>
+        <v>-0.1333</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4093</v>
+        <v>-0.2581</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0558</v>
+        <v>0.1249</v>
       </c>
       <c r="P20" t="n">
-        <v>0.411</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R20" t="n">
-        <v>0.411</v>
+        <v>0.8219</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0281</v>
+        <v>-0.1848</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2795</v>
+        <v>-0.3992</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3075</v>
+        <v>0.2144</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8288</v>
+        <v>2.4657</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8288</v>
+        <v>1.048</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. YOUNG</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,152 +2131,69 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0028</v>
+        <v>6.101200000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9539</v>
+        <v>2.8961</v>
       </c>
       <c r="F21" t="n">
-        <v>1.951</v>
+        <v>3.2049</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0783</v>
+        <v>1.8601</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7343</v>
+        <v>6.202500000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.344</v>
+        <v>-4.342599999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.945</v>
+        <v>6.9544</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4761</v>
+        <v>11.4387</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.4689</v>
+        <v>-4.4844</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1333</v>
+        <v>-5.0944</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2581</v>
+        <v>-5.2361</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1249</v>
+        <v>0.1418000000000004</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2055</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0274</v>
+        <v>-11.3014</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8219</v>
+        <v>11.3015</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1848</v>
+        <v>-2.1287</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3992</v>
+        <v>-2.4621</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2144</v>
+        <v>0.3333</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4657</v>
+        <v>6.369799999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4178</v>
+        <v>9.705299999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>play_by_play_2536320_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>C.B. ZARAGOZA</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>6.101199999999999</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.896100000000001</v>
-      </c>
-      <c r="F22" t="n">
-        <v>3.204899999999999</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.8601</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.2025</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-4.342599999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6.9544</v>
-      </c>
-      <c r="K22" t="n">
-        <v>11.4387</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-4.4844</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-5.0944</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-5.2361</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.1418000000000006</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.775557561562891e-17</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-11.3014</v>
-      </c>
-      <c r="R22" t="n">
-        <v>11.3015</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-2.1287</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-2.4621</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.3332999999999999</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.3698</v>
-      </c>
-      <c r="W22" t="n">
-        <v>9.705299999999999</v>
-      </c>
-      <c r="X22" t="n">
         <v>-3.335599999999999</v>
       </c>
-      <c r="Y22" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
